--- a/path2shock_calculation/input/path.xlsx
+++ b/path2shock_calculation/input/path.xlsx
@@ -7835,16 +7835,16 @@
         <v>1909.0</v>
       </c>
       <c r="E108" s="3">
-        <v>1910.0</v>
+        <v>1908.0</v>
       </c>
       <c r="F108" s="3">
-        <v>1911.0</v>
+        <v>1907.0</v>
       </c>
       <c r="G108" s="3">
-        <v>1912.0</v>
+        <v>1906.0</v>
       </c>
       <c r="H108" s="3">
-        <v>1913.0</v>
+        <v>1905.0</v>
       </c>
       <c r="I108" s="3">
         <v>1914.0</v>
@@ -7859,7 +7859,7 @@
         <v>1917.0</v>
       </c>
       <c r="M108" s="3">
-        <v>1918.0</v>
+        <v>1900.0</v>
       </c>
       <c r="N108" s="3">
         <v>1919.0</v>
@@ -7900,16 +7900,16 @@
         <v>1927.0</v>
       </c>
       <c r="E109" s="3">
-        <v>1928.0</v>
+        <v>1924.0</v>
       </c>
       <c r="F109" s="3">
-        <v>1929.0</v>
+        <v>1921.0</v>
       </c>
       <c r="G109" s="3">
-        <v>1930.0</v>
+        <v>1918.0</v>
       </c>
       <c r="H109" s="3">
-        <v>1931.0</v>
+        <v>1915.0</v>
       </c>
       <c r="I109" s="3">
         <v>1932.0</v>
@@ -7924,7 +7924,7 @@
         <v>1935.0</v>
       </c>
       <c r="M109" s="3">
-        <v>1936.0</v>
+        <v>1908.0</v>
       </c>
       <c r="N109" s="3">
         <v>1937.0</v>
@@ -7965,16 +7965,16 @@
         <v>1945.0</v>
       </c>
       <c r="E110" s="3">
-        <v>1946.0</v>
+        <v>1944.0</v>
       </c>
       <c r="F110" s="3">
-        <v>1947.0</v>
+        <v>1943.0</v>
       </c>
       <c r="G110" s="3">
-        <v>1948.0</v>
+        <v>1942.0</v>
       </c>
       <c r="H110" s="3">
-        <v>1949.0</v>
+        <v>1941.0</v>
       </c>
       <c r="I110" s="3">
         <v>1950.0</v>
@@ -7989,7 +7989,7 @@
         <v>1953.0</v>
       </c>
       <c r="M110" s="3">
-        <v>1954.0</v>
+        <v>1907.0</v>
       </c>
       <c r="N110" s="3">
         <v>1955.0</v>
@@ -8119,7 +8119,7 @@
         <v>1989.0</v>
       </c>
       <c r="M112" s="3">
-        <v>1990.0</v>
+        <v>1980.0</v>
       </c>
       <c r="N112" s="3">
         <v>1991.0</v>

--- a/path2shock_calculation/input/path.xlsx
+++ b/path2shock_calculation/input/path.xlsx
@@ -1657,58 +1657,58 @@
         <v>45</v>
       </c>
       <c r="D13" s="3">
-        <v>199.0</v>
+        <v>199.7</v>
       </c>
       <c r="E13" s="3">
-        <v>200.0</v>
+        <v>200.5</v>
       </c>
       <c r="F13" s="3">
-        <v>201.0</v>
+        <v>201.3</v>
       </c>
       <c r="G13" s="3">
-        <v>202.0</v>
+        <v>202.1</v>
       </c>
       <c r="H13" s="3">
-        <v>203.0</v>
+        <v>202.9</v>
       </c>
       <c r="I13" s="3">
-        <v>204.0</v>
+        <v>203.7</v>
       </c>
       <c r="J13" s="3">
-        <v>205.0</v>
+        <v>204.5</v>
       </c>
       <c r="K13" s="3">
-        <v>206.0</v>
+        <v>205.3</v>
       </c>
       <c r="L13" s="3">
-        <v>207.0</v>
+        <v>206.1</v>
       </c>
       <c r="M13" s="3">
-        <v>208.0</v>
+        <v>206.9</v>
       </c>
       <c r="N13" s="3">
-        <v>209.0</v>
+        <v>207.7</v>
       </c>
       <c r="O13" s="3">
-        <v>210.0</v>
+        <v>208.5</v>
       </c>
       <c r="P13" s="3">
-        <v>211.0</v>
+        <v>209.3</v>
       </c>
       <c r="Q13" s="3">
-        <v>212.0</v>
+        <v>210.1</v>
       </c>
       <c r="R13" s="3">
-        <v>213.0</v>
+        <v>210.9</v>
       </c>
       <c r="S13" s="3">
-        <v>214.0</v>
+        <v>211.7</v>
       </c>
       <c r="T13" s="3">
-        <v>215.0</v>
+        <v>212.5</v>
       </c>
       <c r="U13" s="3">
-        <v>216.0</v>
+        <v>213.3</v>
       </c>
     </row>
     <row r="14">
@@ -4452,58 +4452,58 @@
         <v>120</v>
       </c>
       <c r="D56" s="3">
-        <v>973.0</v>
+        <v>973.9</v>
       </c>
       <c r="E56" s="3">
-        <v>974.0</v>
+        <v>974.1</v>
       </c>
       <c r="F56" s="3">
-        <v>975.0</v>
+        <v>974.3</v>
       </c>
       <c r="G56" s="3">
-        <v>976.0</v>
+        <v>974.5</v>
       </c>
       <c r="H56" s="3">
-        <v>977.0</v>
+        <v>974.7</v>
       </c>
       <c r="I56" s="3">
-        <v>978.0</v>
+        <v>974.9</v>
       </c>
       <c r="J56" s="3">
-        <v>979.0</v>
+        <v>975.1</v>
       </c>
       <c r="K56" s="3">
-        <v>980.0</v>
+        <v>975.3</v>
       </c>
       <c r="L56" s="3">
-        <v>981.0</v>
+        <v>975.5</v>
       </c>
       <c r="M56" s="3">
-        <v>982.0</v>
+        <v>975.7</v>
       </c>
       <c r="N56" s="3">
-        <v>983.0</v>
+        <v>975.9</v>
       </c>
       <c r="O56" s="3">
-        <v>984.0</v>
+        <v>976.100000000001</v>
       </c>
       <c r="P56" s="3">
-        <v>985.0</v>
+        <v>976.300000000001</v>
       </c>
       <c r="Q56" s="3">
-        <v>986.0</v>
+        <v>976.500000000001</v>
       </c>
       <c r="R56" s="3">
-        <v>987.0</v>
+        <v>976.700000000001</v>
       </c>
       <c r="S56" s="3">
-        <v>988.0</v>
+        <v>976.900000000001</v>
       </c>
       <c r="T56" s="3">
-        <v>989.0</v>
+        <v>977.100000000001</v>
       </c>
       <c r="U56" s="3">
-        <v>990.0</v>
+        <v>977.300000000001</v>
       </c>
     </row>
     <row r="57">
